--- a/apps/web/public/Trikosh_Equity_Research_Template.xlsx
+++ b/apps/web/public/Trikosh_Equity_Research_Template.xlsx
@@ -2941,7 +2941,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="str">
-        <v>Net Debt ($mm)</v>
+        <v>Typical range 7–12%. Use Damodaran's WACC by sector at pages.stern.nyu.edu/~adamodar as your starting point.</v>
       </c>
     </row>
     <row r="15">
